--- a/PPP_empirical_reinforcement_bundle_20260416_unified_v3/01_trend_adjusted_DID/tables/trend_adjusted_did_results.xlsx
+++ b/PPP_empirical_reinforcement_bundle_20260416_unified_v3/01_trend_adjusted_DID/tables/trend_adjusted_did_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,13 +514,13 @@
         <v>262</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2262861101927882</v>
+        <v>0.2262861101927911</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1744093771933589</v>
+        <v>0.1744093771934292</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1944790328877616</v>
+        <v>0.1944790328879358</v>
       </c>
       <c r="J2" t="n">
         <v>262</v>
@@ -558,13 +558,13 @@
         <v>262</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.35210675967008</v>
+        <v>-0.3521067596700481</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1784378679689557</v>
+        <v>0.1784378679690451</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04846438271309223</v>
+        <v>0.04846438271322518</v>
       </c>
       <c r="J3" t="n">
         <v>262</v>
@@ -602,13 +602,13 @@
         <v>262</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1699354582537249</v>
+        <v>-0.1699354582534498</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4092905410846794</v>
+        <v>0.4092905410846416</v>
       </c>
       <c r="I4" t="n">
-        <v>0.677999029924208</v>
+        <v>0.6779990299246719</v>
       </c>
       <c r="J4" t="n">
         <v>262</v>
